--- a/meta/1-3-1-a.xlsx
+++ b/meta/1-3-1-a.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист" sheetId="2" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>1. Информация об индикаторе</t>
   </si>
@@ -112,59 +112,270 @@
     <t>+996 (0312) 32 46 52</t>
   </si>
   <si>
-    <t>Численность населения, получающие пенсии или социальные пособия.</t>
-  </si>
-  <si>
-    <t>Получатель пенсионных выплат (пособий) — физическое лицо, которому выплачивается пенсия (пособие). 
-Пенсия – страховая выплата, производимая при наступлении страхового случая застрахованному лицу в размере и на условиях, установленных законодательством о государственном пенсионном социальном страховании.
-Численность получателей пенсий — число лиц на конец (начало) отчетного года, которым назначена ежемесячная денежная сумма на условиях, предусмотренных законодательством о пенсионном обеспечении. Общая численность получателей пенсий отдельно подсчитывается по числу лицевых счетов пенсионеров, состоящих на учете в органах Социального фонда, других министерств и ведомств, а также Негосударственного пенсионного фонда.
-Обязательное социальное обеспечение – система закрепленных в законодательстве социально-экономических мероприятий, гарантирующих материальное обеспечение граждан в старости, при нетрудоспособности, при потере кормильца в семье; обеспечение пособиями семей со сравнительно низкими среднедушевыми доходами, при отсутствии у них права на пенсионное обеспечение.</t>
-  </si>
-  <si>
-    <t>В соответствии с законодательством Кыргызской Республики, определены основы правового регулирования в области установления и применения гарантированных государственных минимальных социальных стандартов для обеспечения важнейших жизненных потребностей населения, включая социальные стандарты в области пенсионного обеспечения населения. 
-Право на пенсии по государственному пенсионному социальному страхованию (далее - пенсии) имеют застрахованные граждане Кыргызской Республики, иностранные граждане и лица без гражданства, проживающие в республике, вносящие взносы на государственное пенсионное социальное страхование на основании и условиях, предусмотренных Законом Кыргызской Республики "О государственном социальном страховании":627}.</t>
-  </si>
-  <si>
-    <t>Административные данные по утвержденным формам государственной статистической отчетности представляют Соцфонд КР, МТСР КР, Накопительный пенсионный фонд КР, Министерства и ведомства, имеющие пенсионные органы.</t>
-  </si>
-  <si>
-    <t>НСК на годовой основе осуществляет сбор и обработку по формам статистической отчетности «Отчет о получателях социальных пособий и суммах назначенных им месячных пособий», «Отчет о численности пенсионеров и суммах назначенных им месячных пенсий», «Отчет о численности пенсионеров, состоящих на учете Накопительного Пенсионного Фонда и суммах назначенных им месячных пенсий», «Отчет о численности пенсионеров, и суммах назначенных пенсий, состоящих на учете в органах силовых структур».</t>
-  </si>
-  <si>
-    <t>Отношение численности пенсионеров, состоящих на учете во всех пенсионных органах и численности граждан, получающих социальное пособие к общей численности населения.</t>
-  </si>
-  <si>
-    <t>Контроль относительно лицевых счетов и сумм, назначенных пенсиий, пособий осуществляют надзорные органы.</t>
-  </si>
-  <si>
-    <t>Данные доступны с 2007 года.</t>
+    <t xml:space="preserve">www.stat.gov.kg  </t>
+  </si>
+  <si>
+    <t>Данные доступны с 2007 года</t>
   </si>
   <si>
     <t>Национальный уровень</t>
   </si>
   <si>
-    <t>Пенсионный возраст в стране устанавливается законодательством КР.</t>
-  </si>
-  <si>
-    <t>Закон КР «О государственном пенсионном социальном страховании»: http://cbd.minjust.gov.kg/act/view/ru-ru/557/310?cl=ru-ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">www.stat.gov.kg  </t>
-  </si>
-  <si>
-    <t>1.3.1.а Доля населения, получающих ЕПМС/«үй-бүлөгө көмөк» к общей численности населения</t>
+    <t xml:space="preserve">• Закон Кыргызской Республики «Об официальной статистике» от 8 июля 2019 года № 82; 
+• Закон Кыргызской Республики от 28 июля 2017 года № 163 «О государственных пособиях в Кыргызской Республике»; 
+• Закон Кыргызской Республики от 3 марта 2023 года № 49 «О правах и гарантиях лиц с ограниченными возможностями здоровья в Кыргызской Республике»; 
+• Постановление Правительства КР от 18 сентября 2018 года № 434 «О назначении и выплате пособий по временной нетрудоспособности, пособий по беременности и родам, ритуальных пособий (на погребение)»; 
+</t>
+  </si>
+  <si>
+    <r>
+      <t>Государственные социальные пособия</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> представляют собой гарантированную Конституцией Кыргызской Республики материальную поддержку малообеспеченным семьям и гражданам, а также нетрудоспособным гражданам при отсутствии права на социальную защиту. Установлены следующие виды государственных пособий: 1) ежемесячное пособие гражданам (семьям), имеющим 3 и более детей в возрасте от 3 до 16 лет " үй-бүлөгө көмөк"; 2) ежемесячное пособие лицам, не имеющим права на пенсионное обеспечение "социальное пособие".                                                                                                                                                                                  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Получатель пособий</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">— физическое лицо, которому выплачивается пособие.  Обязательное социальное обеспечение – система закрепленных в законодательстве социально-экономических мероприятий, гарантирующих материальное обеспечение граждан в старости, при нетрудоспособности, при потере кормильца в семье; обеспечение пособиями семей со сравнительно низкими среднедушевыми доходами, при отсутствии у них права на социальную защиту.        
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Сумма назначенных месячных государственных социальных пособий </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">включает сведения о назначенных социальных пособиях их получателям, включая и получателей, проживающих в домах-интернатах для  инвалидов. Эти суммы подсчитываются по данным лицевых счетов всех получателей социального пособия.  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Средний размер назначенных месячных государственных социальных пособий</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> исчисляется как отношение общей суммы назначенных месячных пособий всем получателям, состоящим на учете в органах социальной защиты, к их общей численности.  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Малообеспеченная семья</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> - семья, имеющая доход на каждого члена семьи ниже гарантированного минимального уровня потребления.  
+Состав семьи - в состав семьи включаются совместно проживающие лица, связанные родственными отношениями, ведущие общее хозяйство и имеющие общий бюджет. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Гарантированный минимальный уровень потребления </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">– это ежегодно устанавливаемый Правительством Кыргызской Республики социальный стандарт, рассчитываемый исходя из бюджета и состояния экономики с учетом минимального потребительского бюджета, позволяющий посредством дотации обеспечивать малообеспеченным семьям и гражданам жизненно необходимый уровень потребления. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>чччччччччччччччччччччччччччччччччччччччччччччччччччччччччччччч</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                     </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Постоянное население </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">- население, постоянно проживающее на момент переписи на данной территории, включая временно отсутствующих. В межпереписной период производится текущая оценка постоянного населения на базе данных переписи и с учетом сведений текущей регистрации демографических событий.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Государственные социальные пособия представляют собой гарантированную Конституцией Кыргызской Республики материальную поддержку малообеспеченным семьям и гражданам, а также нетрудоспособным гражданам при отсутствии права на пенсионное обеспечение. 
+Установлены следующие виды государственных пособий: 
+• единое ежемесячное пособие малообеспеченным семьям и гражданам; 
+• ежемесячное социальное пособие. 
+Ежемесячные социальные пособия выплачиваются следующим лицам: 
+• детям-инвалидам, больным детским церебральным параличом и детям, ВИЧ- инфицированным или больным СПИДом, до 18 лет; 
+• инвалидам с детства I, II и III групп; 
+• инвалидам I, II и III групп - при отсутствии права на пенсионное обеспечение; 
+• престарелым гражданам - при отсутствии права на пенсионное обеспечение; 
+• матерям-героиням - при отсутствии права на пенсионное обеспечение; 
+• детям в случае потери кормильца – при отсутствии права на пенсионное обеспечение. 
+</t>
+  </si>
+  <si>
+    <t>Социальное обслуживание представляют собой услуги медицинского и бытового характера, представляемые органами социальной помощи, нуждающимся в постороннем уходе и помощи на дому либо в стационарых учреждениях. Государственые социальные пособия представляют собой гарантированную Конституцией Кыргызской Респблики материальную поддержку малообеспеченным семьям и гражданам, а также нетрудоспособным гражданам при отсутствии права на пенсионное обеспечение.</t>
+  </si>
+  <si>
+    <t>Для проведения статистического наблюдения используется официальная статистическая отчетность форма №2-собес (госпособия) «Сводный отчет о выплате и потребной сумме единого ежемесячного и социальных пособий».</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Охвату подлежат административные данные ​​Министерство труда, социального обеспечения и миграции КР (МТСОМ).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Метод наблюдения</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – сплошное наблюдение: официальная статистическая отчетность.
+Объектом статистического наблюдения является численность получающих различного рода государственных пособий, а также общие выплаты пособий (по категориям) и средние размеры пособий.
+Единицами наблюдения являются статистические единицы, осуществляющие организацию обязательного социального обеспечения.                                                                                                                                                                                                                                                                                                                </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Основные показатели статистического наблюдения </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Статистика социальной защиты имеет свои специфические показатели для всесторонней характеристики объекта исследования.  
+• численность и состав получающих различного рода государственные пособия, а также общие выплаты пособий (по категориям); 
+• средние размеры  пособий, в том числе по группам получателей; 
+• сеть домов-интернатов для инвалидов, число мест в них и численность лиц, в них проживающих; 
+• размер социальных выплат населению и их соотношение с величиной прожиточного минимума; 
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1.3.1.а Доля населения, получающих  «үй-бүлөгө көмөк» к общей численности населения</t>
+  </si>
+  <si>
+    <t>Доля населения, получающих  пособия «үй-бүлөгө көмөк» к общей численности населения равна: Численность получающих  пособия  «үй-бүлөгө көмөк» делим на Общую численность населения и умножаем на 100%.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -197,6 +408,38 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -239,25 +482,33 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -265,8 +516,16 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -574,12 +833,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Лист1"/>
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="71.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="99.140625" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -589,7 +847,7 @@
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -597,7 +855,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -609,8 +867,8 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>44</v>
+      <c r="B4" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -623,7 +881,7 @@
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>28</v>
       </c>
     </row>
@@ -631,7 +889,7 @@
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -639,7 +897,7 @@
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -647,7 +905,7 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -656,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -665,28 +923,28 @@
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="314.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="257.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
+      <c r="B14" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -695,20 +953,20 @@
       </c>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>36</v>
+      <c r="B17" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -717,27 +975,25 @@
       </c>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>38</v>
-      </c>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -749,32 +1005,30 @@
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>39</v>
+      <c r="B23" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>40</v>
+      <c r="B24" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="1:2" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
